--- a/app/suppliers.xlsx
+++ b/app/suppliers.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="ספקים" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -926,10 +926,8 @@
       <c r="E11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">אישור ת״י רלוונטי / הסמכות / מספר תעודה / רישיון / אישור</t>
-        </is>
+      <c r="F11" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -1004,24 +1002,19 @@
           <t xml:space="preserve">מובילי פלסטיק למתקני חשמל  ותקשורת</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">קיים</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISO 9001 2015</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-05-06</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">קיים</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISO 9001 2015</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
